--- a/data/trans_camb/IQ26A_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IQ26A_R2-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>6,19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,88</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,53</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-2,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,88</t>
+          <t>-6,43; 10,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,76</t>
+          <t>-9,63; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 19,62</t>
+          <t>-14,0; -2,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,83</t>
+          <t>-4,62; 5,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 4,13</t>
+          <t>0,29; 13,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -2,53</t>
+          <t>-3,91; 23,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 6,01</t>
+          <t>-3,26; 7,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,68</t>
+          <t>-3,37; 6,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,89</t>
+          <t>-6,74; 4,54</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-44,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>44,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>240,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>63,03%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-44,16%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-64,7%</t>
+          <t>-58,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-64,89; 456,81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-67,06; 356,12</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-47,76; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,03; 259,13</t>
+          <t>-52,7; 292,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 300,16</t>
+          <t>-50,35; 282,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 305,34</t>
+          <t>-100,0; 352,11</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,88</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,91</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,68</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,21</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,02</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,41</t>
+          <t>-2,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 12,43</t>
+          <t>-1,24; 12,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 23,57</t>
+          <t>10,74; 26,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 13,65</t>
+          <t>-9,17; 7,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 12,72</t>
+          <t>-4,54; 12,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 25,79</t>
+          <t>4,58; 23,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 6,17</t>
+          <t>-10,38; 15,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 10,19</t>
+          <t>0,22; 11,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 22,09</t>
+          <t>10,78; 22,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 3,95</t>
+          <t>-9,18; 5,52</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>70,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>227,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-48,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>29,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>101,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-12,57%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>227,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-50,1%</t>
+          <t>-4,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>-26,93%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 129,04</t>
+          <t>-13,25; 253,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 242,7</t>
+          <t>85,74; 563,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,32; 142,08</t>
+          <t>-100,0; 159,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 271,77</t>
+          <t>-24,89; 127,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,6; 519,19</t>
+          <t>25,75; 241,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,57</t>
+          <t>-71,75; 155,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 124,14</t>
+          <t>1,84; 144,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,26; 269,85</t>
+          <t>80,72; 275,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 47,52</t>
+          <t>-76,15; 60,09</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-14,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-17,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-17,75</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-15,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-17,86</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-14,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-17,75</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,75</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,7</t>
+          <t>-11,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,29; -8,26</t>
+          <t>-23,05; -7,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,26; -11,24</t>
+          <t>-25,63; -11,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 10,44</t>
+          <t>-26,68; -11,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,08; -6,76</t>
+          <t>-24,97; -8,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,88; -11,58</t>
+          <t>-27,75; -11,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,94; -11,53</t>
+          <t>-18,56; 11,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,97; -9,65</t>
+          <t>-20,64; -9,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,29; -12,96</t>
+          <t>-23,18; -12,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -2,45</t>
+          <t>-19,17; -1,68</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-83,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-87,84%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-83,27%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-38,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-85,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-85,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-65,76%</t>
+          <t>-65,11%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -49,89</t>
+          <t>-96,19; -49,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-83,96; 90,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-95,9; -40,8</t>
+          <t>-100,0; -43,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>-83,71; 109,06</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-95,03; -66,49</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-95,31; -64,55</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 1,54</t>
+          <t>-91,01; -4,4</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15,1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,47</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5,25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18,36</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13,44</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,1</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,79</t>
+          <t>16,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,54</t>
+          <t>24,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 13,14</t>
+          <t>3,74; 23,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 14,93</t>
+          <t>5,59; 24,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 48,21</t>
+          <t>1,31; 68,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,22; 23,28</t>
+          <t>-5,76; 12,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 25,82</t>
+          <t>-4,35; 13,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 63,61</t>
+          <t>-2,52; 45,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 15,82</t>
+          <t>1,86; 15,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 17,62</t>
+          <t>3,9; 17,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 44,65</t>
+          <t>7,51; 48,87</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>149,49%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>167,92%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>397,33%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>48,41%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>169,2%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>149,49%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>167,92%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>331,31%</t>
+          <t>149,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>238,15%</t>
+          <t>249,71%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 204,62</t>
+          <t>22,54; 486,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 237,36</t>
+          <t>30,64; 470,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 578,18</t>
+          <t>-11,68; 1200,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,71; 440,05</t>
+          <t>-43,18; 186,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,22; 488,21</t>
+          <t>-30,57; 201,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 1093,43</t>
+          <t>-30,23; 585,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,94; 219,7</t>
+          <t>13,11; 218,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,45; 241,28</t>
+          <t>25,45; 247,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,28; 579,79</t>
+          <t>62,22; 622,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>59,44</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,62</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>76,68</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,15</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,94</t>
+          <t>76,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>67,66</t>
+          <t>67,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 17,71</t>
+          <t>-1,65; 15,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 11,44</t>
+          <t>-11,13; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,48; 91,3</t>
+          <t>37,79; 82,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 15,01</t>
+          <t>-1,57; 16,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 0,0</t>
+          <t>-4,75; 12,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,21; 79,17</t>
+          <t>53,42; 92,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,78</t>
+          <t>1,02; 13,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,02</t>
+          <t>-4,86; 4,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52,06; 80,45</t>
+          <t>52,12; 81,01</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>229,45%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1887,71%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>209,59%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>48,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2310,73%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>229,45%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1871,81%</t>
+          <t>2312,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2094,77%</t>
+          <t>2103,55%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,24; —</t>
+          <t>-53,83; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594,91; —</t>
+          <t>385,19; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,87; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>485,0; —</t>
+          <t>598,23; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,67; 1291,79</t>
+          <t>-3,84; 1211,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>800,34; 8611,71</t>
+          <t>849,11; 8784,34</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-5,98</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-3,25</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-4,1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-12,67</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-12,83</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-9,18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-5,98</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-3,25</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>-9,22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-7,52</t>
+          <t>-7,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-21,87; -2,61</t>
+          <t>-11,87; -0,75</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -3,76</t>
+          <t>-9,63; 4,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 14,59</t>
+          <t>-10,53; 7,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -0,09</t>
+          <t>-22,07; -4,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 4,08</t>
+          <t>-22,52; -3,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 5,29</t>
+          <t>-20,33; 17,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,07; -4,48</t>
+          <t>-15,08; -4,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -2,18</t>
+          <t>-14,13; -2,39</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 2,86</t>
+          <t>-13,42; 4,36</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-81,16%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-44,13%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-55,58%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-75,15%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-76,11%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-54,48%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-81,16%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-44,13%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-61,02%</t>
+          <t>-54,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-62,9%</t>
+          <t>-59,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-93,94; -8,28</t>
+          <t>-100,0; 157,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-93,75; -16,11</t>
+          <t>-89,95; 169,34</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 149,79</t>
+          <t>-100,0; 225,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,71</t>
+          <t>-93,38; -6,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-87,89; 164,83</t>
+          <t>-93,47; -15,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 198,43</t>
+          <t>-100,0; 159,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-94,07; -38,55</t>
+          <t>-94,74; -38,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-87,75; -10,24</t>
+          <t>-87,57; -17,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,44</t>
+          <t>-100,0; 83,8</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-10,52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10,13</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>29,87</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-9,06</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>13,11</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>41,97</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-10,52</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,13</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,53</t>
+          <t>37,88</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>35,73</t>
+          <t>33,12</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-15,85; -3,09</t>
+          <t>-16,36; -4,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5,76; 21,12</t>
+          <t>2,47; 17,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25,89; 59,81</t>
+          <t>13,98; 46,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-16,15; -4,8</t>
+          <t>-15,37; -3,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,13; 17,34</t>
+          <t>4,96; 21,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,78; 47,84</t>
+          <t>22,95; 54,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -6,06</t>
+          <t>-14,17; -5,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6,12; 17,18</t>
+          <t>6,3; 16,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>25,0; 46,4</t>
+          <t>22,07; 44,04</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-71,02%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>68,41%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>201,65%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-62,71%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>90,77%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>290,58%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-71,02%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>212,83%</t>
+          <t>262,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>244,18%</t>
+          <t>226,32%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-83,16; -20,3</t>
+          <t>-86,35; -40,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>28,77; 189,86</t>
+          <t>12,95; 158,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>150,7; 546,34</t>
+          <t>79,7; 392,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-87,14; -40,56</t>
+          <t>-83,16; -26,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,41; 148,67</t>
+          <t>26,15; 188,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>89,89; 400,19</t>
+          <t>128,4; 451,1</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-80,71; -47,11</t>
+          <t>-81,25; -47,51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>35,26; 144,21</t>
+          <t>33,88; 134,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>150,39; 370,61</t>
+          <t>132,53; 349,62</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-6,77</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-13,15</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,16</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-9,02</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-17,48</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-6,77</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-13,46</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-0,84</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-15,0</t>
+          <t>-14,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 5,01</t>
+          <t>-7,51; 6,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,57; -3,27</t>
+          <t>-12,66; 0,07</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -13,1</t>
+          <t>-19,82; -3,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 6,26</t>
+          <t>-7,83; 6,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-13,18; -0,59</t>
+          <t>-14,87; -2,69</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-19,55; -3,9</t>
+          <t>-22,73; -13,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,06</t>
+          <t>-5,93; 3,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,49; -3,5</t>
+          <t>-11,68; -2,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,32; -9,04</t>
+          <t>-19,1; -8,33</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-2,95%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-37,87%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-73,5%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-6,64%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-51,61%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-2,95%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-37,87%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-75,26%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>-4,74%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-84,83%</t>
+          <t>-83,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 36,85</t>
+          <t>-35,43; 42,98</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-69,43; -21,01</t>
+          <t>-60,56; 0,13</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>-100,0; -10,46</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>-38,29; 44,95</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>-70,24; -19,43</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>-32,47; 43,29</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>-62,15; -3,5</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -11,71</t>
-        </is>
-      </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 26,14</t>
+          <t>-28,75; 24,34</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -22,61</t>
+          <t>-59,14; -18,83</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -47,28</t>
+          <t>-100,0; -43,22</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2,41</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-3,13</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>10,59</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,97</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,15</t>
+          <t>-3,91; 1,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,97</t>
+          <t>-0,53; 5,29</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4,8; 18,08</t>
+          <t>1,58; 12,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,92</t>
+          <t>-6,06; -0,03</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,57</t>
+          <t>-1,95; 4,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,5</t>
+          <t>4,06; 17,42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,14</t>
+          <t>-3,97; 0,01</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,86</t>
+          <t>-0,36; 4,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,83; 12,27</t>
+          <t>3,96; 12,6</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-8,56%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>54,43%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-22,98%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>77,67%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-8,56%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -0,51</t>
+          <t>-30,23; 15,99</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 32,64</t>
+          <t>-4,16; 49,25</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>34,29; 142,83</t>
+          <t>11,39; 113,79</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 19,13</t>
+          <t>-40,28; -0,82</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 51,08</t>
+          <t>-12,82; 34,68</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,11; 109,75</t>
+          <t>27,11; 137,37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-29,49; -1,21</t>
+          <t>-28,75; -0,34</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 33,23</t>
+          <t>-2,56; 33,42</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>29,2; 101,06</t>
+          <t>29,18; 103,04</t>
         </is>
       </c>
     </row>
